--- a/光伏配储项目/电价数据/2026/彩虹站.xlsx
+++ b/光伏配储项目/电价数据/2026/彩虹站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.51662</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.3799</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.9427300000000001</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.59721</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.7696000000000001</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.6353099999999999</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.60984</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43768</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45425</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44053</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42287</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.42782</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40845</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39752</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.39924</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38393</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40175</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42286</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41161</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35354</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39096</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38448</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41601</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39249</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42178</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41297</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42297</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41254</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44389</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.38605</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30349</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.33445</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.26104</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.30153</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.32403</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.50017</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.44117</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.25487</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.17237</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.23147</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.26815</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.2942</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.09825</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.19769</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.39766</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.39214</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.30652</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.18654</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>-0.02142</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.24561</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.08529</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.18736</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.24369</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.26914</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.23931</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.46527</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.33053</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.06995999999999999</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.29745</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.16918</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.39369</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.40807</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.48874</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.43403</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.41048</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.57709</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>1.07508</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>1.15771</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>1.10824</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.50307</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.88566</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.6435299999999999</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.5317200000000001</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.61771</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.74624</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.68368</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.961</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.11142</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.82378</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.86676</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.21796</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.62379</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.9186</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.7680800000000001</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.55965</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.88193</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.80871</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.8506900000000001</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.8244199999999999</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.57462</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47944</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.40166</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41308</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42233</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.3299</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.85994</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.83856</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.87513</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.53607</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.52249</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.5062300000000001</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.5374099999999999</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.498</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.41199</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47259</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.38939</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38088</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39202</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33759</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37075</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35598</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35958</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37549</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37546</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35943</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38044</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.42123</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.52024</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.65347</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.7241000000000001</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.44076</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.3837</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.4482</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34592</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.3414</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.59745</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.68555</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.3315</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.42492</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.5293600000000001</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.30702</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.46276</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.38719</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.39185</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.46309</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.33293</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.6741</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.71027</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.99907</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.37996</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.63307</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.69164</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.5744900000000001</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.6147400000000001</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.9737100000000001</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.7252000000000001</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.48606</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.57957</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.2942</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.35361</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.46075</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.3606</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.36198</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.80286</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.57275</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.5021</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.56063</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.56621</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.38525</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.4075299999999999</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.6652899999999999</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.5667000000000001</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.49796</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.72651</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.51513</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.99282</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.1543</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.07087</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.8983099999999999</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.9961599999999999</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.97977</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>1.14142</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.8265</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.90154</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.13164</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.56939</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.34634</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.5010899999999999</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.49557</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.6559199999999999</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44075</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43476</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.41812</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33935</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37745</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35456</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33353</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.51561</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.39557</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.50341</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.39687</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.39528</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40561</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.39548</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38952</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38259</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36188</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43387</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44993</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33556</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37018</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39348</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36632</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37091</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35325</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.3586</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.34855</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36308</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35618</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38021</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39645</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47352</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.4501</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44427</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34836</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39704</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36837</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34681</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.47784</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.40736</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.43987</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.39605</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.3606</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.45321</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.30633</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.30877</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31199</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.30279</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.34175</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.35121</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.57055</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.5583400000000001</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.78792</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.44248</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.66388</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.7559</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.41935</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.40949</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.47452</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.50825</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.57168</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.5455599999999999</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.4088</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.3317</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.34813</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.32481</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.33764</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.56288</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.5688500000000001</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.5900599999999999</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.76583</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>1.1454</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.66169</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.16681</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.60733</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.55298</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.47428</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.57839</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.86949</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.84849</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.78463</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.5348999999999999</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.7691399999999999</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.6930299999999999</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.94297</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.62588</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.87821</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.6187699999999999</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.6396499999999999</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.62571</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.64344</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.5777</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.666</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.60082</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.5080899999999999</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.5131599999999999</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.42345</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.35889</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34312</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31991</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.59545</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.48975</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.36523</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.40132</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.42448</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.40544</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.34808</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.3844</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.32968</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.32199</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.31778</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.46676</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.32474</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.31842</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.31779</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.32762</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.32014</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.30528</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.30496</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.30337</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.30087</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.30227</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33922</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35781</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.35142</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38918</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.32635</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.33817</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.31734</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.36171</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.34358</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.42312</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.34959</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.36729</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.50571</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.47823</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.37933</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.41251</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.49536</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.33907</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.44075</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.7431</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.7113400000000001</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.4839</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.60194</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.38648</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.28187</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.25104</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.38876</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.33775</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.31982</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.4708</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.6897799999999999</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.27776</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.35396</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.47115</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.45193</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.46044</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.42439</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.4334</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.39563</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.32043</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.68511</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.41845</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.82363</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.4125</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.35242</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.42031</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.46209</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.42745</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.46977</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.54412</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.5330199999999999</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.59138</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.5600499999999999</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.793</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.546</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.5179199999999999</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.45136</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.46478</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.4802</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.48513</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.45558</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.4469</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.38684</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.32965</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.3159</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.39114</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.30062</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.30805</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31276</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.30218</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.30021</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.36277</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.40217</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.3873</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35791</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34033</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.3064</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.31454</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.31576</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.30868</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.3071</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.29296</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30844</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.30667</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.29238</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.29566</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.29413</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.29469</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.29569</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.30113</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29562</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29792</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31253</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.30669</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31648</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32443</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33281</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32611</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.28675</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.27108</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.10861</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.10883</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.11107</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.08676</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.08231000000000001</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.09257</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.08502</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.10218</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.01181</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.01533</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.01878</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.05696</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.07464</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.0438</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.05524</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.00704</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.0591</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.00579</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.07218000000000001</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.05433</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.00634</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.03527</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.03433</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.03104</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.03912</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.02036</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.21154</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.08468000000000001</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.08609</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.0895</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.00049</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.00417</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.04491</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>0.00266</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.20714</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.10797</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.16436</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.31364</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.34476</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.34521</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.34032</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.34092</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.35877</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.37329</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.34408</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.35535</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.39977</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.39275</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.40073</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37537</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.35121</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39955</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39843</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40989</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46754</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35788</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39643</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40002</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.45659</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.3447</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.37394</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.75337</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.48774</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.52961</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.44914</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.44514</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.36565</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.36753</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.36441</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33816</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.31531</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32743</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.36366</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35672</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.35131</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34644</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33605</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31859</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33149</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33625</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.3246</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.30517</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32461</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34245</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31602</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.13108</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04794</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04658</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>0.00425</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04484</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04318</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.04169</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.03066</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.12768</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.01061</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.04336</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.00507</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.01882</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04294</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04283</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04491</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0448</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04485</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.03626</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04229</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04458</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.0421</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04231</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>0.00437</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04448</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04476</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04249</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04346</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.00571</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.00405</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.04989</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>0.005849999999999999</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>0.00393</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>0.00513</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>0.00777</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>0.00821</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.22667</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.18374</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.31363</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.30724</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.31557</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.31024</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.30601</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.3156</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.32537</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.30951</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.30991</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.30816</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.31101</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.28495</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.3107200000000001</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.32008</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.32286</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.3192</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.31162</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.3196</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.32723</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.35651</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.35296</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.3675</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36599</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33622</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.3354</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31283</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40554</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.35058</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32164</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31645</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30459</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.2869</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29847</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29413</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.29258</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28651</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27745</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27649</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28563</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.19197</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.17982</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.1718</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14841</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16014</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15938</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23744</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.2148</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.23796</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.27469</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28976</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29481</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32029</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29552</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28679</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28734</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28697</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27681</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28744</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32356</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31418</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.31104</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.32914</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.38298</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.44655</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.37639</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.34872</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.43172</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.44294</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.51202</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45603</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33661</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.42588</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.4651</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.44701</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.48162</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.35043</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.34045</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.32507</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.32511</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.1536</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29257</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31203</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.32174</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31099</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.4049700000000001</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.37245</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.3826</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.42118</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.4794</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.54471</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79237</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.64899</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.43364</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.53886</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.82112</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>1.00186</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.55302</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>1.00641</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.97065</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.39314</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.4424</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.9853500000000001</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.7026399999999999</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.30493</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.96411</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.8289</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.41896</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.11234</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.58688</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.80545</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5303600000000001</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.78776</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.78908</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87859</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.88146</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.50674</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.41216</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.41738</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.4654700000000001</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.22448</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87937</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55135</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.63947</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5426599999999999</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.50261</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.4579</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42625</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.44018</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45069</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.39256</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45284</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42073</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35401</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.4001</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36529</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38932</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41494</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43395</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39062</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.3537</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.34849</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.35349</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40659</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.35544</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.4509</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35597</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.39777</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40013</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.5892200000000001</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42923</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59624</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.59722</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.6613</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.5386799999999999</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.44827</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.5660499999999999</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.46915</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.9615199999999999</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.6893400000000001</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.91444</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.89576</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.9089400000000001</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.36609</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.48266</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.36343</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.37423</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.34132</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.42671</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.49731</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.35764</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.33852</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.3493</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.46349</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.41281</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.5662200000000001</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.38431</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.38739</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.34313</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.36357</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.37027</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.39351</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.36009</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.36596</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.37362</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.35551</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.36444</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.36295</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.34935</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.36126</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.36879</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.3855</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.36679</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.39342</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.37611</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.37608</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.40111</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.38592</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.38209</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.37796</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.37385</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.36316</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.34513</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.42353</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41258</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45231</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41493</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39145</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37491</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35327</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32928</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.95636</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36058</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.47701</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.4079</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.48258</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.54522</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.39262</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.40968</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.39194</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.41464</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.38378</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.3538</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.3858</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.40008</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50008</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35721</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38769</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35531</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.39351</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.35929</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.35569</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.3638</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.39911</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.42676</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.37658</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.22601</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.40685</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.39559</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.43052</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.39514</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.36799</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.38216</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.38822</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.22671</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.31621</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.27497</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.34217</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.2928</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.3223</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.40862</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.52524</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.44213</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.38071</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.45892</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.39759</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.38949</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.3636</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.49758</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.3772799999999999</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.30734</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.32153</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.33438</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.32802</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29865</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.35224</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.26806</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32291</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.30368</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.35454</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.29271</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.28794</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.34506</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.24212</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.31479</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.30229</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.32275</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.36379</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.02377</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.43249</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.29281</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35984</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44783</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.32313</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42044</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35897</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40172</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40045</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59676</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35006</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.9331</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.4355</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.19351</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.70362</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.79538</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.64981</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.58368</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45034</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50049</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.4399</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43746</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41504</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42352</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5005500000000001</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43408</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41293</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43413</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39041</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42803</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45042</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39631</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.4235</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43413</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40027</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42355</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.3966</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.4025</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.56029</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.37784</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.41676</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.6474800000000001</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.48913</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.44594</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.35921</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.51075</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.36431</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.51575</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.3224</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>0.82233</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.68837</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.5710700000000001</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.43356</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.30915</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>0.7395900000000001</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.74471</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.44075</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.43881</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.42724</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.6432100000000001</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.66215</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.47787</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.28658</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.31339</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.38353</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.45186</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.35816</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.45429</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.41135</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.40813</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.40063</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.40545</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.45796</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.44675</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.42723</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.46712</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.5686</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.49386</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.45399</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.4853</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.4392799999999999</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.44124</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.5456799999999999</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.48715</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.46044</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.49794</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.45028</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.43792</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.75454</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.5660599999999999</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.90712</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.64823</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.5247000000000001</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.47894</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.4754</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38651</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36959</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33455</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34093</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32956</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32473</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31898</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42523</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.33944</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34425</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33595</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32618</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32944</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32622</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32494</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32414</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32746</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32618</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31601</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32016</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32014</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.3102200000000001</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32514</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31121</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.31925</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32052</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39152</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32508</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34996</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.40001</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33882</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35489</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33219</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33457</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.30049</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33466</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.34887</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.30827</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.33145</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>0.96047</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.31467</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.26505</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.18087</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.18507</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.31471</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.19588</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.57859</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.58792</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.17082</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.17656</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.19113</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.18874</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.29479</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.19778</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.30578</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.30815</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.18591</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.17692</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.16767</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.17064</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.20141</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.19437</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.1823</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.30887</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.33489</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.34143</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.33955</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.40271</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.32724</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.3744</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.36149</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.4052</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34364</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37994</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.40023</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36071</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38492</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.44973</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.39981</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39356</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40189</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39773</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.44333</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43993</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.43929</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44421</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44428</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40267</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.39054</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39772</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.3916</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35975</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36039</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34805</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34934</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.54243</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38909</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46869</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42387</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41594</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37014</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38109</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38021</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39308</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37993</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36988</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38025</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39109</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37024</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.38027</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35028</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34724</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35527</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34489</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.3402</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34519</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.3402</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34476</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35517</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.37019</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38011</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.35994</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.33999</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34024</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34032</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32935</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34444</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.35156</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.37558</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.28921</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31344</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31312</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.31049</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.28632</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.28526</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.30247</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.26112</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.2726</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.25638</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.2286</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.24891</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.29823</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.28984</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31385</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.29164</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.29404</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.32738</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.30349</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.30249</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.28599</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.26459</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31423</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.31004</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.31411</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.30079</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.30926</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.3669</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.44567</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.41896</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.41224</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.46871</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.57977</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.5566</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.47794</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.37888</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.36098</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.37993</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.45918</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.51579</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.58031</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.58316</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.45353</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.40734</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.39739</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.37568</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.36814</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.36171</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.4195</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.39254</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.39021</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.39184</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.38329</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.38037</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38031</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38036</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38532</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36026</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36606</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41861</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37069</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.44646</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38047</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35276</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36022</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35175</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34198</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34778</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.3458</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34919</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34629</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.34919</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34015</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.3414</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34292</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33813</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33807</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33982</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33062</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34165</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.34461</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.39512</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.34277</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.46247</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.34121</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.35379</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.53696</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.54347</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.53218</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.5346000000000001</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.72517</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.71278</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.48486</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.58999</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.84033</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.51689</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.82453</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.70451</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.6972200000000001</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.76463</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.2143</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.5682999999999999</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.27467</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.81456</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.28688</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.53722</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.31698</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.56041</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.52543</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.6968099999999999</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.6798999999999999</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.71328</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.72662</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.72175</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.6989099999999999</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.72337</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.5991799999999999</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.75652</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.87209</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.83784</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.8156100000000001</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.7534299999999999</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.7611599999999999</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.76924</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.71688</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.80352</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.52463</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.56114</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.74725</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.75561</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.7495299999999999</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>1.04959</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.82892</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>1.14559</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.77913</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.87478</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.49288</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.43606</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.37531</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>1.46198</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>1.16705</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.79139</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.55338</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.34063</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.34206</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.38052</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.32244</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.33084</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.32166</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.31174</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.31533</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.39397</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.5660299999999999</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.33931</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.3288</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.3348</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.3463</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.33468</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.33097</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.33366</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32515</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.33032</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32846</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.3265</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32744</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32769</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33096</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32605</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32084</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31974</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32636</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33024</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33517</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34592</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34074</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34232</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.3368</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33872</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.3258</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.33057</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33814</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.58273</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.58721</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33773</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.35743</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.45631</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.37177</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.38371</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.38128</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33831</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.28956</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.3423</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34173</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.2985</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32497</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28171</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.3292</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.32517</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32111</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.3299</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32848</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33355</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.3353</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.31403</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.33149</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.3222</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.3278</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.32513</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.34363</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.38201</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.50148</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.66062</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.59048</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.51466</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.4584</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.37417</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35006</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.39071</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.37996</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.38349</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.37974</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.41258</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36761</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36148</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36777</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.3624</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37308</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36202</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39284</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38553</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37162</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.40286</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35499</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.3799</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.36941</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36096</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35024</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34933</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34931</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35128</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35527</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35537</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35135</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34943</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34938</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34623</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.35972</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34702</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34963</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33704</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36928</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.3383</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33665</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33962</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33588</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34945</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33632</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32806</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34852</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.36082</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33596</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.3582</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.29297</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.33207</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.3289</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.3282</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32984</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.32157</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32755</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.32174</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.32014</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.3351</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32577</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32964</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31878</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37105</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32975</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.36161</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.45633</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.35173</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.38535</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.76044</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.38187</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.34859</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.35369</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.36102</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.33784</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33183</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33864</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.3456</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.37895</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.56236</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.3891</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.3546</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.37775</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.39494</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35128</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.37326</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34729</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36029</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36022</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36226</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.3502</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.47263</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.40244</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.40406</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38363</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.42965</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40916</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38572</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.38502</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65197</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.83084</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.47176</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.40087</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45943</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.3934</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35066</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35096</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35957</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34477</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.31274</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41077</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37582</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37089</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36136</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35918</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35917</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36235</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.3589</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36057</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35357</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36062</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35678</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35235</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35976</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.33976</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37085</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.3565</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37945</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.3799</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35649</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35814</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34972</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32988</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.32915</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.34929</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.3539</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.28668</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.20115</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.39292</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.2942</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.29302</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.22257</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.33193</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.28743</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.28934</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.01502</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.3235</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.24641</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.29785</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.22153</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.32301</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.02741</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.3444700000000001</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.18815</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.30954</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.05196</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.31465</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.27762</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.32322</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.31477</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.45131</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>1.47908</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.5508099999999999</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>1.38932</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.48825</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.5167999999999999</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.96711</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.48381</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.9477599999999999</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>1.36964</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>1.31959</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>1.65478</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>1.44734</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>1.51562</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>1.00704</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>1.57536</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>1.44188</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>1.01805</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.91123</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.5569500000000001</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.60302</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.61141</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.43004</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.41896</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37805</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37448</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.3673</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36015</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34534</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.5443600000000001</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.75198</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.66395</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.91589</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41942</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.4049700000000001</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40494</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.41137</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.40904</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41775</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.40006</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39588</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41165</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.40939</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39366</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38712</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.4185</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38727</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41663</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.39008</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.3999</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.39986</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41249</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.39991</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.45051</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.44949</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.5606</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.50066</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.45069</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.35124</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.41908</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.79501</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.7896299999999999</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>1.09499</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.16208</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.26846</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.37642</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.322</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>1.18638</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.68348</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.71093</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.80289</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.55804</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.5482100000000001</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.5628099999999999</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.37306</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.34449</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>-0.009089999999999999</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>-0.02358</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.2164</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.28279</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.99117</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>1.68719</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>1.45095</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>1.05829</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.58484</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.5245</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.43795</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.60414</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.29738</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.46162</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.57696</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.36755</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.37046</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.41294</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.40236</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.46704</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.54625</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.44906</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.5203099999999999</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.4363</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.53464</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.57728</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.739</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.68743</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.64238</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.64351</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.6274</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.76239</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>1.01507</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.47089</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>1.13706</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>1.05783</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.8107000000000001</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.38057</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.85011</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.78567</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.63687</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>1.0233</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.64928</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.72637</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.59315</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47841</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.47175</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.4194</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.55344</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.40135</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.40105</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.45813</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43679</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42655</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44836</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41783</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40083</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.4577</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39934</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40704</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39862</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38854</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37486</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36585</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37679</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37125</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.3602</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36585</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38657</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39025</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37958</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36647</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36137</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35511</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.3796</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.40936</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.40284</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.39114</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.4383</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39448</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38659</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35163</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36857</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.38122</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.42998</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.42077</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.43564</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.45296</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.58261</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.69592</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.31201</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.13032</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.1769</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.1876</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.37194</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.32645</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.02931</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.30931</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29941</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.31344</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35262</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.35477</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34874</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.36631</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.40669</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.4035</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.41693</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.43494</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.42066</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36372</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.4131</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.41672</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.44707</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.428</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.45185</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38078</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38625</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40611</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40198</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34409</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36548</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37798</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39922</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37947</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39964</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.3808</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37501</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36026</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39388</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37907</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36415</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.33115</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.50643</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.51185</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.46073</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.43046</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.38753</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37715</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35055</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37706</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.3732</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.3563</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35512</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.35123</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35749</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34738</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35075</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.3486</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.35139</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33144</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33973</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34038</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33546</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.3404700000000001</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34548</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33089</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33048</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33739</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33746</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.35129</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.32875</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.32072</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.31642</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.32501</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.36545</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.3305</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.32429</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.32015</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.25416</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.3049</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.27051</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.24831</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.26504</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.03954999999999999</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.19249</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.29181</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.29691</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.07042</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.18088</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04336</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.2774</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.17865</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.18933</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.06269</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.3112799999999999</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.0182</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.24082</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.24889</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.17304</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.23319</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27884</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.31654</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.27051</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.31403</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.33635</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.30415</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.3625</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34664</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.3694</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.42216</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.39202</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.35608</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.34462</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.41175</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.39664</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.36761</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.32044</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.41233</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.37005</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.42487</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.37722</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.39561</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.38822</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.39277</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.36784</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.38458</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.41395</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34759</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36513</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.36984</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.36558</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34951</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.34996</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.35014</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.3517</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32295</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.40937</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33842</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34423</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.35582</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.34675</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.33107</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32475</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.31968</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31936</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.31049</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.31028</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31062</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.31096</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31097</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31088</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.31659</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30682</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30682</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30931</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.30989</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30615</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30682</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30741</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.31051</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31137</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.29656</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.25877</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.25234</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.16908</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.20796</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.45343</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.08990999999999999</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.07568999999999999</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.03537</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>0.02331</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.18936</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.03551</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>0.03457</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>0.02137</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>0.11248</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>0.18716</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>0.12192</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>0.04767</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>0.03694</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>0.03495</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>0.11108</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>0.01961</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.02636</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>0.02203</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>0.01976</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>0.0288</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.08789</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.05538000000000001</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>0.01941</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>0.02213</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>0.01943</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>0.01874</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>0.03196</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>0.02253</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>0.05716</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>0.03833</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.16957</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.20724</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.25204</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.29405</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.27433</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.27863</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.27154</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.27652</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.28929</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.31101</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.29395</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.29695</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.28487</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.3122200000000001</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.30219</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.30399</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.29322</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.3055</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.29272</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.30756</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.29751</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.3239</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.45605</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.31609</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.33296</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.30427</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.2799</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.28777</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.27547</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.26596</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.22729</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.13031</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.5338200000000001</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.26639</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.1625</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.31597</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.2783</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.3122200000000001</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.25176</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.31005</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.29057</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.2775899999999999</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.25838</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.24121</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.22875</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.24672</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.25316</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.2167</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.25166</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.2459</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.25844</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.26832</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.26805</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.24618</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.28641</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.26136</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.30145</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.40236</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.30243</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.27354</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.32948</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.22287</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.14485</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.6133500000000001</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.61634</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.7273500000000001</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.57385</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.2945</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.46471</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.15572</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.26762</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.14937</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.11974</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>1.09127</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.15424</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.27801</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.14605</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.31398</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.11884</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.01426</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.12233</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.1799</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.05219</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.19921</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.03398</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.13973</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.28765</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.23582</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.08595</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.17943</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.31561</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.49388</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.1709</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.40102</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.39089</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.51836</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.4758</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.49261</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.49304</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.49236</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.53299</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.41668</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.51274</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.43116</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.5357499999999999</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.92663</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.68332</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.66796</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.70448</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.82437</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.68377</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.7113200000000001</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.72265</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.8181499999999999</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.55245</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.54667</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.5456</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.65396</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.56157</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.47317</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.34555</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.3407</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.41366</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.34958</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32899</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.39561</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.45466</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.38283</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.42041</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.42042</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.37662</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.35858</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.35662</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.34869</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.34895</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.34032</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.34179</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.33309</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.3449700000000001</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.14086</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.33779</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.33453</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.3274</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.33485</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.33404</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.33915</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.34818</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.34796</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.35865</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.96285</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.76274</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.6645800000000001</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.61409</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.49408</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.58163</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.4994</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.43741</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>1.0605</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.6212300000000001</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.53371</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.62421</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.6946</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.6891900000000001</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.54486</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.56263</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.44924</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.36276</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.36184</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.41244</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.32521</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.16175</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.36643</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.28539</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.35277</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.36309</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.2239</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.38697</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.56774</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.32484</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.16357</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.35702</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.33185</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.34821</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.34969</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.35768</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.3575</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.36863</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.37447</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.38905</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.39398</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.38667</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.39317</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.37177</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.37934</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.35373</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.38785</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.40457</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.39447</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.42819</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.5468200000000001</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.54191</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.42964</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.36751</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.76247</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.49098</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.48829</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.55453</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.52786</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.40986</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.41152</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.4001</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.38242</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.38804</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.32923</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.3450299999999999</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32987</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33341</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.3334</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37039</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.36328</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.35814</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.30725</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.33969</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.33954</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.34815</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.33577</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.34364</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.34939</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.34527</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34772</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.31103</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.35028</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34328</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.34466</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.32932</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.3348</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34651</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33569</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34225</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.3555</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32724</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36911</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35668</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.37314</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35941</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.42704</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.5534199999999999</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.34598</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.43475</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.54237</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.77571</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.68441</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.9105800000000001</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>1.01383</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.38792</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.49975</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.5362</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.48224</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.45584</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.4896</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.46852</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.45719</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>1.30255</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.46037</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.32305</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.62414</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.35505</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.45161</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.35912</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.47991</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.47865</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.15136</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.46048</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.41248</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.47157</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.49718</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.49044</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.52599</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.6366000000000001</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.6591900000000001</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.7060599999999999</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.77259</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.75578</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.8258</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.83828</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.81601</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.6977899999999999</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.60163</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.58548</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.47222</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.70297</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.5383</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.6116</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.53871</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.57245</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.5482400000000001</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.51212</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.53554</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.42415</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.6835</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.5022099999999999</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.40149</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45845</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.45887</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38015</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.50252</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.47431</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37271</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.36268</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36868</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.5618500000000001</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.4012</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40124</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39192</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38075</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37554</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37441</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37864</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37729</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36916</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36691</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36152</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35586</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32883</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35618</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35105</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37102</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.39958</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37575</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36966</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.37691</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.39343</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.47084</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.39131</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.6045900000000001</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.6008</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.58361</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.65734</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.6659299999999999</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.57067</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.7065900000000001</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.77566</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.5156900000000001</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.33096</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.51575</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.44286</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.52391</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.50664</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.50676</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.24736</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.24807</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.26678</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.48373</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.45624</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.32425</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.34187</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.42813</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.19994</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.47766</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.5513400000000001</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.53442</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.42024</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.60085</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.60319</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.42102</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.62413</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.4246</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.40622</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.43816</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.72942</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.65386</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.6012799999999999</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.5820299999999999</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.46712</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.5406299999999999</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.51385</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.51434</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.33671</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.45948</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.55016</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.53427</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.27444</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.671</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.53399</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.48384</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.4621</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.33634</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.7387400000000001</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.50558</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.50736</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39829</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.49867</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.47676</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.43959</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.38292</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36944</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37505</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27077</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.3711</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.33102</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37039</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33997</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.34043</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34984</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.3274</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33897</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.40625</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.34186</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.3407</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.36165</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.34206</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.34108</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.34163</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.32091</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.33195</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.32578</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.31854</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.31583</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.31788</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.31782</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.30803</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.30538</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.35001</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.38487</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.3188</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.30392</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.29897</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.29475</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.28807</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.32778</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.35383</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.43844</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.39944</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.3292</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.35561</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.57297</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.4757</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.7688400000000001</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.25989</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.18982</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>1.1438</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.7612000000000001</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.66104</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.18391</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.07840999999999999</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>-0.00869</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.09861</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.07654999999999999</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.24623</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.00487</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.20329</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.09032</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.20818</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.32629</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.19353</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.13604</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.30416</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.31204</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.24314</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.50306</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.50656</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.38806</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.35308</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.31281</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.44923</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.52515</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.57702</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.45131</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.46419</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.37394</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.44567</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.45627</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.16447</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.02973</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.26988</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.28891</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.41151</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.31275</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.42896</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.51498</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.49534</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.50086</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.53034</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.5151100000000001</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.4969</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.6267999999999999</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.47923</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.49971</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.45037</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.43634</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.38494</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.37827</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.3753</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.99801</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.50341</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.55845</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.6050599999999999</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.46338</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.38515</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.3618</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.38478</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.35446</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.35549</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.34833</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.37865</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.36533</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38007</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.35543</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.36255</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36386</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.36332</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36566</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.35896</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.3659</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35039</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.38338</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.34517</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.33476</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.31418</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.31423</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.30853</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.38502</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.42013</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.40568</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.38714</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.40757</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.37567</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.41308</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.5438999999999999</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.3141</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.29022</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.3342</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.32681</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.2347</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.4326</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.26704</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.07993</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.07689</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.12851</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.08065</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.15869</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.45005</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.22431</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.31587</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.28192</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.39761</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.19626</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.2818</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.33632</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>1.13706</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.8959600000000001</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.35896</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.8273200000000001</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.42176</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.68991</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>1.09253</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>1.16031</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>1.00104</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.83482</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.57017</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.49541</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.74052</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.75347</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.53399</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.73054</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.55325</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.5873200000000001</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.578</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.56333</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.7496</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.62151</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.62395</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.63225</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.7516499999999999</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.5313</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.55455</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.50288</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.57559</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.6851499999999999</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.73588</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.5474</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.43089</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.40557</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.40408</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.33413</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.66791</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.43695</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.43989</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.33895</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.38797</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.38222</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.38088</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.36668</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41964</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.36229</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.38874</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37333</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.35399</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.35276</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35018</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33352</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.32678</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.3504</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.32462</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.32773</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.33469</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.34229</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.36228</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.3465</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.34552</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.31477</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.27816</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.25407</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.23658</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.16602</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.21946</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.2978</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.26327</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.2384</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.35085</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.29956</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.22324</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.18929</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.22761</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.22351</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.20839</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.13375</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.14981</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.19042</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.14486</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.1944</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.15708</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.26842</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.22619</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.1737</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.11405</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.33686</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.19113</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.2094</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.27209</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.20833</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.48104</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.30286</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.30285</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.34324</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.37964</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.34117</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.35696</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.38078</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.38312</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.38642</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.39872</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.44501</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.46895</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.42092</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.43202</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.34473</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.34615</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.5177999999999999</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.34643</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.46461</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.45146</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.42698</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.43581</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.53974</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.56059</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.50842</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.44152</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.44795</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.42271</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.40411</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.40849</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.40967</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38407</v>
       </c>
     </row>
   </sheetData>
